--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/2707-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/2707-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6A4FE48A-B2D0-43DE-96FF-C01C74ED534B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9805B473-0CD2-457E-BC18-625161FBECE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{0FA16891-74A3-4B2D-926C-8751E4C6D946}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{F8ABF19F-E23B-4D38-8EC8-9369E5466D67}"/>
   </bookViews>
   <sheets>
     <sheet name="2707-dividend-20260225_0_4" sheetId="1" r:id="rId1"/>
@@ -1529,23 +1529,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A682781C-6056-42FE-A9C4-7D3D321802D5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3DE5923E-008C-47EC-BCA7-B4E835508DF6}">
   <dimension ref="A1:R74"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="7.33203125" customWidth="1"/>
-    <col min="3" max="3" width="8.6640625" customWidth="1"/>
-    <col min="4" max="6" width="8.33203125" customWidth="1"/>
-    <col min="7" max="8" width="8" customWidth="1"/>
-    <col min="9" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.6640625" customWidth="1"/>
+    <col min="1" max="1" width="6.5" customWidth="1"/>
+    <col min="2" max="2" width="9.25" customWidth="1"/>
+    <col min="3" max="3" width="10.75" customWidth="1"/>
+    <col min="4" max="6" width="10.5" customWidth="1"/>
+    <col min="7" max="8" width="10" customWidth="1"/>
+    <col min="9" max="10" width="10.5" customWidth="1"/>
+    <col min="11" max="13" width="10" customWidth="1"/>
+    <col min="14" max="14" width="10.5" customWidth="1"/>
+    <col min="15" max="17" width="10" customWidth="1"/>
+    <col min="18" max="18" width="10.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
@@ -1573,7 +1573,7 @@
       <c r="Q1" s="31"/>
       <c r="R1" s="23"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="24" t="s">
         <v>1</v>
       </c>
@@ -1603,7 +1603,7 @@
       <c r="Q2" s="33"/>
       <c r="R2" s="34"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="24" t="s">
         <v>2</v>
       </c>
@@ -1649,7 +1649,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="26"/>
       <c r="B4" s="27"/>
       <c r="C4" s="7"/>
@@ -1699,7 +1699,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="38">
         <v>2026</v>
       </c>
@@ -1753,7 +1753,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>26</v>
       </c>
@@ -1809,7 +1809,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="40">
         <v>2025</v>
       </c>
@@ -1863,7 +1863,7 @@
         <v>6.81</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="17" t="s">
         <v>26</v>
       </c>
@@ -1919,7 +1919,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
         <v>26</v>
       </c>
@@ -1975,7 +1975,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="17" t="s">
         <v>26</v>
       </c>
@@ -2031,7 +2031,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="17" t="s">
         <v>26</v>
       </c>
@@ -2087,7 +2087,7 @@
         <v>6.81</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="17" t="s">
         <v>26</v>
       </c>
@@ -2143,7 +2143,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="38">
         <v>2024</v>
       </c>
@@ -2197,7 +2197,7 @@
         <v>5.07</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
         <v>26</v>
       </c>
@@ -2253,7 +2253,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>26</v>
       </c>
@@ -2309,7 +2309,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
         <v>26</v>
       </c>
@@ -2365,7 +2365,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>26</v>
       </c>
@@ -2421,7 +2421,7 @@
         <v>5.07</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
         <v>26</v>
       </c>
@@ -2477,7 +2477,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="40">
         <v>2023</v>
       </c>
@@ -2531,7 +2531,7 @@
         <v>2.94</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="17" t="s">
         <v>26</v>
       </c>
@@ -2587,7 +2587,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="17" t="s">
         <v>26</v>
       </c>
@@ -2643,7 +2643,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="17" t="s">
         <v>26</v>
       </c>
@@ -2699,7 +2699,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="17" t="s">
         <v>26</v>
       </c>
@@ -2755,7 +2755,7 @@
         <v>2.94</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="17" t="s">
         <v>26</v>
       </c>
@@ -2811,7 +2811,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="38">
         <v>2022</v>
       </c>
@@ -2865,7 +2865,7 @@
         <v>7.14</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
         <v>26</v>
       </c>
@@ -2921,7 +2921,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
         <v>26</v>
       </c>
@@ -2977,7 +2977,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="11" t="s">
         <v>26</v>
       </c>
@@ -3033,7 +3033,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
         <v>26</v>
       </c>
@@ -3089,7 +3089,7 @@
         <v>7.14</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="11" t="s">
         <v>26</v>
       </c>
@@ -3145,7 +3145,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="11" t="s">
         <v>26</v>
       </c>
@@ -3201,7 +3201,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="40">
         <v>2021</v>
       </c>
@@ -3255,7 +3255,7 @@
         <v>3.08</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="17" t="s">
         <v>26</v>
       </c>
@@ -3311,7 +3311,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="17" t="s">
         <v>26</v>
       </c>
@@ -3367,7 +3367,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="17" t="s">
         <v>26</v>
       </c>
@@ -3423,7 +3423,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="17" t="s">
         <v>26</v>
       </c>
@@ -3479,7 +3479,7 @@
         <v>3.08</v>
       </c>
     </row>
-    <row r="37" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="17" t="s">
         <v>26</v>
       </c>
@@ -3535,7 +3535,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="17" t="s">
         <v>26</v>
       </c>
@@ -3591,7 +3591,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="38">
         <v>2020</v>
       </c>
@@ -3645,7 +3645,7 @@
         <v>2.67</v>
       </c>
     </row>
-    <row r="40" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="11" t="s">
         <v>26</v>
       </c>
@@ -3701,7 +3701,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="11" t="s">
         <v>26</v>
       </c>
@@ -3757,7 +3757,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="11" t="s">
         <v>26</v>
       </c>
@@ -3813,7 +3813,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="11" t="s">
         <v>26</v>
       </c>
@@ -3869,7 +3869,7 @@
         <v>2.67</v>
       </c>
     </row>
-    <row r="44" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A44" s="40">
         <v>2019</v>
       </c>
@@ -3923,7 +3923,7 @@
         <v>9.6</v>
       </c>
     </row>
-    <row r="45" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A45" s="17" t="s">
         <v>26</v>
       </c>
@@ -3979,7 +3979,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A46" s="17" t="s">
         <v>26</v>
       </c>
@@ -4035,7 +4035,7 @@
         <v>3.73</v>
       </c>
     </row>
-    <row r="47" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A47" s="17" t="s">
         <v>26</v>
       </c>
@@ -4091,7 +4091,7 @@
         <v>5.86</v>
       </c>
     </row>
-    <row r="48" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A48" s="38">
         <v>2018</v>
       </c>
@@ -4145,7 +4145,7 @@
         <v>4.6399999999999997</v>
       </c>
     </row>
-    <row r="49" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A49" s="40">
         <v>2017</v>
       </c>
@@ -4199,7 +4199,7 @@
         <v>4.9800000000000004</v>
       </c>
     </row>
-    <row r="50" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A50" s="38">
         <v>2016</v>
       </c>
@@ -4253,7 +4253,7 @@
         <v>4.66</v>
       </c>
     </row>
-    <row r="51" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A51" s="40">
         <v>2015</v>
       </c>
@@ -4307,7 +4307,7 @@
         <v>4.17</v>
       </c>
     </row>
-    <row r="52" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A52" s="38">
         <v>2014</v>
       </c>
@@ -4361,7 +4361,7 @@
         <v>2.54</v>
       </c>
     </row>
-    <row r="53" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A53" s="40">
         <v>2013</v>
       </c>
@@ -4415,7 +4415,7 @@
         <v>2.61</v>
       </c>
     </row>
-    <row r="54" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A54" s="38">
         <v>2012</v>
       </c>
@@ -4469,7 +4469,7 @@
         <v>3.77</v>
       </c>
     </row>
-    <row r="55" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A55" s="40">
         <v>2011</v>
       </c>
@@ -4523,7 +4523,7 @@
         <v>2.0499999999999998</v>
       </c>
     </row>
-    <row r="56" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A56" s="38">
         <v>2010</v>
       </c>
@@ -4577,7 +4577,7 @@
         <v>2.0299999999999998</v>
       </c>
     </row>
-    <row r="57" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A57" s="40">
         <v>2009</v>
       </c>
@@ -4631,7 +4631,7 @@
         <v>2.56</v>
       </c>
     </row>
-    <row r="58" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A58" s="38">
         <v>2008</v>
       </c>
@@ -4685,7 +4685,7 @@
         <v>2.4900000000000002</v>
       </c>
     </row>
-    <row r="59" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A59" s="40">
         <v>2007</v>
       </c>
@@ -4739,7 +4739,7 @@
         <v>3.7</v>
       </c>
     </row>
-    <row r="60" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A60" s="38">
         <v>2006</v>
       </c>
@@ -4793,7 +4793,7 @@
         <v>4.5599999999999996</v>
       </c>
     </row>
-    <row r="61" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A61" s="40">
         <v>2005</v>
       </c>
@@ -4847,7 +4847,7 @@
         <v>4.96</v>
       </c>
     </row>
-    <row r="62" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A62" s="38">
         <v>2004</v>
       </c>
@@ -4901,7 +4901,7 @@
         <v>6.27</v>
       </c>
     </row>
-    <row r="63" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A63" s="40">
         <v>2003</v>
       </c>
@@ -4955,7 +4955,7 @@
         <v>14.3</v>
       </c>
     </row>
-    <row r="64" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A64" s="38">
         <v>2002</v>
       </c>
@@ -5009,7 +5009,7 @@
         <v>4.87</v>
       </c>
     </row>
-    <row r="65" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A65" s="40">
         <v>2001</v>
       </c>
@@ -5063,7 +5063,7 @@
         <v>7.89</v>
       </c>
     </row>
-    <row r="66" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A66" s="38">
         <v>2000</v>
       </c>
@@ -5117,7 +5117,7 @@
         <v>5.0999999999999996</v>
       </c>
     </row>
-    <row r="67" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A67" s="40">
         <v>1999</v>
       </c>
@@ -5171,7 +5171,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A68" s="38">
         <v>1998</v>
       </c>
@@ -5225,7 +5225,7 @@
         <v>5.33</v>
       </c>
     </row>
-    <row r="69" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A69" s="40">
         <v>1997</v>
       </c>
@@ -5279,7 +5279,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="70" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A70" s="38">
         <v>1996</v>
       </c>
@@ -5333,7 +5333,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="71" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A71" s="40">
         <v>1995</v>
       </c>
@@ -5387,7 +5387,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="72" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A72" s="38">
         <v>1994</v>
       </c>
@@ -5441,7 +5441,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="73" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A73" s="40">
         <v>1993</v>
       </c>
@@ -5495,7 +5495,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="74" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A74" s="38" t="s">
         <v>61</v>
       </c>
